--- a/docs/detail-design/15_ThemSuaNhanVien.xlsx
+++ b/docs/detail-design/15_ThemSuaNhanVien.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="172">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · THÊM / SỬA NHÂN VIÊN</t>
   </si>
@@ -135,13 +135,19 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Ô lỗi viền đỏ + hộp lỗi "Vui lòng nhập đủ các ô bắt buộc" khi lưu; giới hạn độ dài ô chữ (CCCD tối đa 20 ký tự).</t>
+  </si>
+  <si>
     <t>Ảnh 1. Thêm nhân viên (đã bấm Tạo ngẫu nhiên)</t>
   </si>
   <si>
     <t>Ảnh 2. Tên đăng nhập, mật khẩu sai quy tắc</t>
   </si>
   <si>
-    <t>Bấm Tạo tài khoản khi form chưa hợp lệ: dòng gợi ý dưới ô chuyển màu đỏ, không gửi.</t>
+    <t>Bấm Tạo tài khoản khi form chưa hợp lệ: ô lỗi viền đỏ, dòng gợi ý dưới ô chuyển màu đỏ, đầu form hiện hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ)." (ngoài vùng ảnh), không gửi.</t>
   </si>
   <si>
     <t>Ảnh 3. Sửa nhân viên</t>
@@ -207,7 +213,7 @@
     <t>Có</t>
   </si>
   <si>
-    <t>Tối đa 100 ký tự (backend); bỏ khoảng trắng đầu cuối.</t>
+    <t>Tối đa 100 ký tự (frontend maxlength + backend); bỏ khoảng trắng đầu cuối.</t>
   </si>
   <si>
     <t>Số điện thoại</t>
@@ -219,7 +225,7 @@
     <t>form.controls.phone</t>
   </si>
   <si>
-    <t>Tối đa 20 ký tự (backend).</t>
+    <t>Tối đa 20 ký tự (frontend maxlength + backend).</t>
   </si>
   <si>
     <t>CCCD</t>
@@ -234,7 +240,7 @@
     <t>Không</t>
   </si>
   <si>
-    <t>Chỉ chữ số và khoảng trắng (frontend + backend "Chỉ gồm chữ số"). Bỏ khoảng trắng rồi mã hoá AES; chỉ hiện 4 số cuối.</t>
+    <t>Chỉ chữ số và khoảng trắng (frontend + backend "Chỉ gồm chữ số"), tối đa 20 ký tự. Bỏ khoảng trắng rồi mã hoá AES; chỉ hiện 4 số cuối.</t>
   </si>
   <si>
     <t>Placeholder "12 số"</t>
@@ -450,7 +456,7 @@
     <t>2. Lưu</t>
   </si>
   <si>
-    <t>Form không hợp lệ: đánh dấu đã chạm (gợi ý tên đăng nhập / mật khẩu chuyển đỏ), không gửi.</t>
+    <t>Form không hợp lệ: đánh dấu đã chạm (ô lỗi viền đỏ, gợi ý tên đăng nhập / mật khẩu chuyển đỏ), hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", con trỏ tới ô lỗi đầu tiên, không gửi.</t>
   </si>
   <si>
     <t>Thêm: POST /api/accounts — tên đăng nhập trùng → 409; kiểm tra quy tắc mật khẩu; lưu hash BCrypt, mustChangePassword theo ô chọn. Nhật ký ACCOUNT_CREATED "Thêm tài khoản {họ tên} ({tên đăng nhập}), vai trò {…}".</t>
@@ -508,6 +514,15 @@
   </si>
   <si>
     <t>Dữ liệu không hợp lệ (errors: "3–50 ký tự: chữ không dấu, số, dấu chấm, gạch", "Chỉ gồm chữ số", "Tối đa 100 ký tự"…)</t>
+  </si>
+  <si>
+    <t>Thiếu ô bắt buộc / sai quy tắc</t>
+  </si>
+  <si>
+    <t>frontend</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đủ các ô bắt buộc (viền đỏ).</t>
   </si>
   <si>
     <t>Tài khoản không tồn tại</t>
@@ -1141,7 +1156,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1872,8 +1887,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1913,6 +1970,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1932,7 +1993,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1968,7 +2029,7 @@
     </row>
     <row r="45" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -2002,9 +2063,9 @@
       <c r="AF45" s="4"/>
       <c r="AG45" s="4"/>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="46" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -2040,7 +2101,7 @@
     </row>
     <row r="64" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -2076,7 +2137,7 @@
     </row>
     <row r="108" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -2137,7 +2198,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2173,10 +2234,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2187,22 +2248,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2210,12 +2271,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2228,33 +2289,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2262,12 +2323,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2275,38 +2336,38 @@
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="4" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2314,12 +2375,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2327,38 +2388,38 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="5" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="7">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2366,12 +2427,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2384,33 +2445,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2418,12 +2479,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2436,33 +2497,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2470,12 +2531,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2488,33 +2549,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2522,12 +2583,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2540,33 +2601,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2574,12 +2635,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2592,33 +2653,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2626,12 +2687,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2644,33 +2705,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2678,12 +2739,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2696,33 +2757,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2730,12 +2791,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2748,33 +2809,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2782,12 +2843,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2800,33 +2861,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2834,12 +2895,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2852,33 +2913,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2886,12 +2947,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2904,33 +2965,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -2938,12 +2999,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2953,7 +3014,7 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -2989,10 +3050,10 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -3003,22 +3064,22 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -3026,12 +3087,12 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
@@ -3044,33 +3105,33 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -3078,12 +3139,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -3096,33 +3157,33 @@
         <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -3130,12 +3191,12 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -3145,7 +3206,7 @@
     </row>
     <row r="23" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -3181,10 +3242,10 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -3195,22 +3256,22 @@
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P24" s="5"/>
       <c r="Q24" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3218,12 +3279,12 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
       <c r="Y24" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z24" s="5"/>
       <c r="AA24" s="5"/>
       <c r="AB24" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC24" s="5"/>
       <c r="AD24" s="5"/>
@@ -3236,33 +3297,33 @@
         <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3270,12 +3331,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3288,33 +3349,33 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -3322,12 +3383,12 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -3337,7 +3398,7 @@
     </row>
     <row r="28" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -3373,10 +3434,10 @@
     </row>
     <row r="29" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -3387,22 +3448,22 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P29" s="5"/>
       <c r="Q29" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R29" s="5"/>
       <c r="S29" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3410,12 +3471,12 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
       <c r="AB29" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
@@ -3428,33 +3489,33 @@
         <v>19</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -3462,12 +3523,12 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
       <c r="AB30" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3675,7 +3736,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG20"/>
+  <dimension ref="B1:AG21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3684,7 +3745,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3720,7 +3781,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3756,10 +3817,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3794,10 +3855,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3832,7 +3893,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3866,12 +3927,12 @@
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -3906,10 +3967,10 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -3944,10 +4005,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -3982,10 +4043,10 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -4020,10 +4081,10 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -4058,7 +4119,7 @@
     </row>
     <row r="13" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -4094,7 +4155,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -4108,11 +4169,11 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
@@ -4134,7 +4195,7 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4152,7 +4213,7 @@
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -4174,7 +4235,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4192,7 +4253,7 @@
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -4214,7 +4275,7 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4232,7 +4293,7 @@
       </c>
       <c r="O17" s="7"/>
       <c r="P17" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -4254,7 +4315,7 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4272,7 +4333,7 @@
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -4294,7 +4355,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4307,12 +4368,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="7">
-        <v>404</v>
-      </c>
-      <c r="O19" s="7"/>
+      <c r="N19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -4334,7 +4395,7 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4347,12 +4408,12 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O20" s="3"/>
+      <c r="N20" s="7">
+        <v>404</v>
+      </c>
+      <c r="O20" s="7"/>
       <c r="P20" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -4372,8 +4433,48 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="35">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="C3:AG3"/>
@@ -4406,6 +4507,9 @@
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:AG20"/>
+    <mergeCell ref="B21:M21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:AG21"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
